--- a/data/Country_Master.xlsx
+++ b/data/Country_Master.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://apparelme-my.sharepoint.com/personal/138925_appareluae_com/Documents/LS Retail - Masters/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://apparelme-my.sharepoint.com/personal/138925_appareluae_com/Documents/F&amp;B Sales Dashboard - Project/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_F25DC773A252ABDACC10483D51196DB85BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69329921-8301-431B-8160-DB74E8DF492C}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_F25DC773A252ABDACC10483D51196DB85BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A35E2EE0-B743-4695-9E82-6B9E21D09C3E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6770" yWindow="2350" windowWidth="11760" windowHeight="6160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Country_Master_tbl" sheetId="1" r:id="rId1"/>
@@ -33,21 +33,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
   <si>
-    <t>Sr_No_CountryCode</t>
-  </si>
-  <si>
-    <t>Country_Code</t>
-  </si>
-  <si>
-    <t>Country_Name</t>
-  </si>
-  <si>
-    <t>Country_ISO_Code</t>
-  </si>
-  <si>
-    <t>Country_PhoneCode</t>
-  </si>
-  <si>
     <t>AE</t>
   </si>
   <si>
@@ -82,6 +67,21 @@
   </si>
   <si>
     <t>Kuwait</t>
+  </si>
+  <si>
+    <t>country_sr_no</t>
+  </si>
+  <si>
+    <t>country_code</t>
+  </si>
+  <si>
+    <t>country_name</t>
+  </si>
+  <si>
+    <t>country_iso_code</t>
+  </si>
+  <si>
+    <t>country_phone_code</t>
   </si>
 </sst>
 </file>
@@ -415,19 +415,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -435,13 +435,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -449,13 +449,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -463,13 +463,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -477,13 +477,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -491,13 +491,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -505,13 +505,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
